--- a/outputs/run_all_summary/run_all_rw3_summary.xlsx
+++ b/outputs/run_all_summary/run_all_rw3_summary.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>graphs_brand_region</t>
+          <t>sheet_ProducerUA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_brand_region</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_producerua</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -476,7 +476,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>graphs_correlations_lags</t>
+          <t>sheet_ConsumerUA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_correlations_lags</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_consumerua</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -494,7 +494,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>graphs_decomposition</t>
+          <t>sheet_EU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_decomposition</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_eu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -512,7 +512,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>graphs_overlay_ln</t>
+          <t>sheet_ProZorro</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_overlay_ln</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_prozorro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -530,7 +530,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>model_ardl</t>
+          <t>sheet_Silpo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_ardl</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_silpo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -548,7 +548,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>model_discounts</t>
+          <t>sheet_Novus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_discounts</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_novus</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -566,7 +566,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>model_ecm</t>
+          <t>sheet_CME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_ecm</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_cme</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>model_forecast_knn</t>
+          <t>model_short_chain_regional</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_forecast_knn</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/primary_chain_summary</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -602,7 +602,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>model_intersection_bidirectional</t>
+          <t>model_ardl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_intersection_bidirectional</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_ardl</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -620,7 +620,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>model_nardl</t>
+          <t>model_ecm</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_nardl</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_ecm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -638,7 +638,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>model_short_chain_regional</t>
+          <t>model_nardl</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_short_chain_regional</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_nardl</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -666,7 +666,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_vecm</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_vecm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -674,7 +674,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sheet_cme</t>
+          <t>model_discounts</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_cme</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_discounts</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -692,7 +692,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sheet_consumerua</t>
+          <t>model_intersection_bidirectional</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_consumerua</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_intersection_bidirectional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -710,7 +710,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sheet_eu</t>
+          <t>model_forecast_knn</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_eu</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_forecast_knn</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -728,7 +728,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sheet_novus</t>
+          <t>graphs_decomposition</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_novus</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_decomposition</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -746,7 +746,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sheet_producerua</t>
+          <t>graphs_overlay_ln</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_producerua</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_overlay_ln</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -764,7 +764,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sheet_prozorro</t>
+          <t>graphs_correlations_lags</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_prozorro</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_correlations_lags</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -782,7 +782,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sheet_silpo</t>
+          <t>graphs_brand_region</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_silpo</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_brand_region</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_brand_region</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_brand_region</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -905,7 +905,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_correlations_lags</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_correlations_lags</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -944,7 +944,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_decomposition</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_decomposition</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -983,7 +983,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_overlay_ln</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_overlay_ln</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_ardl</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_ardl</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_discounts</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_discounts</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_ecm</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_ecm</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_forecast_knn</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_forecast_knn</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_intersection_bidirectional</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_intersection_bidirectional</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_nardl</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_nardl</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_short_chain_regional</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/primary_chain_summary</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1269,21 +1269,21 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_report.pdf</t>
+          <t>primary_chain_consolidated.pdf</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_report.md</t>
+          <t>primary_chain_consolidated.md</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_vecm</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_vecm</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1329,12 +1329,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sheet_cme</t>
+          <t>sheet_CME</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_cme</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_cme</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1368,12 +1368,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sheet_consumerua</t>
+          <t>sheet_ConsumerUA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_consumerua</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_consumerua</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1407,12 +1407,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sheet_eu</t>
+          <t>sheet_EU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_eu</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_eu</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1446,12 +1446,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sheet_novus</t>
+          <t>sheet_Novus</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_novus</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_novus</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1485,12 +1485,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sheet_producerua</t>
+          <t>sheet_ProZorro</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_producerua</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_prozorro</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1503,33 +1503,33 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>sheet_producerua_output.xlsx</t>
+          <t>sheet_prozorro_output.xlsx</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>sheet_producerua_report.pdf</t>
+          <t>sheet_prozorro_report.pdf</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>sheet_producerua_report.md</t>
+          <t>sheet_prozorro_report.md</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sheet_prozorro</t>
+          <t>sheet_ProducerUA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_prozorro</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_producerua</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1542,33 +1542,33 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>sheet_prozorro_output.xlsx</t>
+          <t>sheet_producerua_output.xlsx</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>sheet_prozorro_report.pdf</t>
+          <t>sheet_producerua_report.pdf</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>sheet_prozorro_report.md</t>
+          <t>sheet_producerua_report.md</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sheet_silpo</t>
+          <t>sheet_Silpo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_silpo</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_silpo</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1610,7 +1610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -2088,24 +2088,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>model_ardl</t>
+          <t>model_discounts</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>model_ardl_output.xlsx</t>
+          <t>model_discounts_output.xlsx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Model_Series</t>
+          <t>Silpo_Discounts_Depth</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3765</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2127,14 +2127,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Silpo_Discounts_Depth</t>
+          <t>Silpo_Discounts_Occurrence</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2156,14 +2156,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Silpo_Discounts_Occurrence</t>
+          <t>Silpo_Transmission_PromoCtrl</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2175,24 +2175,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>model_discounts</t>
+          <t>model_ecm</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>model_discounts_output.xlsx</t>
+          <t>model_ecm_output.xlsx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Silpo_Transmission_PromoCtrl</t>
+          <t>ECM_Summary</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2204,59 +2204,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>model_ecm</t>
+          <t>model_forecast_knn</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>model_ecm_output.xlsx</t>
+          <t>model_forecast_knn_output.xlsx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ARDL_Summary</t>
+          <t>Forecast_Predictions</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>540</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>model_ecm</t>
+          <t>model_forecast_knn</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>model_ecm_output.xlsx</t>
+          <t>model_forecast_knn_output.xlsx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ECM_Summary</t>
+          <t>Forecast_Summary</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2272,20 +2272,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Forecast_Predictions</t>
+          <t>Synthetic_Influence_Coefficient</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>540</v>
+        <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2301,14 +2301,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Forecast_Summary</t>
+          <t>Synthetic_Retail_Series</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>91758</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Synthetic_Influence_Coefficient</t>
+          <t>Synthetic_to_Consumer_Link</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>7</v>
@@ -2359,14 +2359,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Synthetic_Retail_Series</t>
+          <t>Ultimate_Consumer_Price</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>91758</v>
+        <v>145</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2378,30 +2378,30 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>model_forecast_knn</t>
+          <t>model_intersection_bidirectional</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>model_forecast_knn_output.xlsx</t>
+          <t>model_intersection_bidirectional_output.xlsx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Synthetic_to_Consumer_Link</t>
+          <t>Bidirectional_Granger</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2417,14 +2417,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bidirectional_Granger</t>
+          <t>Bidirectional_Results</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2446,20 +2446,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bidirectional_Results</t>
+          <t>CrossTable_Correlations</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2475,14 +2475,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CrossTable_Correlations</t>
+          <t>Intersection_Combination_Detail</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2504,43 +2504,43 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Intersection_Combination_Detail</t>
+          <t>Intersection_Combination_Summar</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>model_intersection_bidirectional</t>
+          <t>model_nardl</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>model_intersection_bidirectional_output.xlsx</t>
+          <t>model_nardl_output.xlsx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Intersection_Combination_Summar</t>
+          <t>NARDL_Summary</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2552,30 +2552,30 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>model_nardl</t>
+          <t>model_short_chain_regional</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>model_nardl_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NARDL_Summary</t>
+          <t>Consolidated_Eligibility</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2586,19 +2586,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chain_Effects_Details</t>
+          <t>Consolidated_ModelCoefficients</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2615,22 +2615,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chain_Effects_Summary</t>
+          <t>Consolidated_PreTests</t>
         </is>
       </c>
       <c r="D35" t="n">
+        <v>144</v>
+      </c>
+      <c r="E35" t="n">
         <v>12</v>
       </c>
-      <c r="E35" t="n">
-        <v>14</v>
-      </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -2644,25 +2644,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LagMatrix_ByProduct</t>
+          <t>Consolidated_ResidualDiagnostic</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2673,19 +2673,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LagProfiles_ByProduct</t>
+          <t>Rule_Documentation</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1025</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2697,53 +2697,53 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>model_short_chain_regional</t>
+          <t>model_vecm</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>model_vecm_output.xlsx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Models_ShortRun_Summary</t>
+          <t>VECM_Summary</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>model_short_chain_regional</t>
+          <t>sheet_CME</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>sheet_cme_output.xlsx</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Prozorro_Regional_Effects_Matri</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>171</v>
+        <v>1023</v>
       </c>
       <c r="E39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2755,24 +2755,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>model_short_chain_regional</t>
+          <t>sheet_CME</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>sheet_cme_output.xlsx</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Prozorro_Regional_Models</t>
+          <t>daily_variants</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1486</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2784,24 +2784,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>model_short_chain_regional</t>
+          <t>sheet_CME</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>sheet_cme_output.xlsx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ShortRun_Details</t>
+          <t>descriptive_stats</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2813,36 +2813,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>model_vecm</t>
+          <t>sheet_CME</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>model_vecm_output.xlsx</t>
+          <t>sheet_cme_output.xlsx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VECM_Summary</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>1023</v>
       </c>
       <c r="E42" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sheet_cme</t>
+          <t>sheet_CME</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2852,14 +2852,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>series_long</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>1023</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sheet_cme</t>
+          <t>sheet_CME</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2881,43 +2881,43 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>daily_variants</t>
+          <t>tests</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1486</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sheet_cme</t>
+          <t>sheet_ConsumerUA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>sheet_cme_output.xlsx</t>
+          <t>sheet_consumerua_output.xlsx</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>descriptive_stats</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>5463</v>
       </c>
       <c r="E45" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2929,24 +2929,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sheet_cme</t>
+          <t>sheet_ConsumerUA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>sheet_cme_output.xlsx</t>
+          <t>sheet_consumerua_output.xlsx</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>daily_variants</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1023</v>
+        <v>5463</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2958,24 +2958,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sheet_cme</t>
+          <t>sheet_ConsumerUA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>sheet_cme_output.xlsx</t>
+          <t>sheet_consumerua_output.xlsx</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>series_long</t>
+          <t>descriptive_stats</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1023</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2987,36 +2987,36 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>sheet_cme</t>
+          <t>sheet_ConsumerUA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>sheet_cme_output.xlsx</t>
+          <t>sheet_consumerua_output.xlsx</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>tests</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>5463</v>
       </c>
       <c r="E48" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>sheet_consumerua</t>
+          <t>sheet_ConsumerUA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3026,14 +3026,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>series_long</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>5463</v>
+        <v>16389</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sheet_consumerua</t>
+          <t>sheet_ConsumerUA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3055,43 +3055,43 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>daily_variants</t>
+          <t>tests</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5463</v>
+        <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>sheet_consumerua</t>
+          <t>sheet_EU</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>sheet_consumerua_output.xlsx</t>
+          <t>sheet_eu_output.xlsx</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>descriptive_stats</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="D51" t="n">
+        <v>111299</v>
+      </c>
+      <c r="E51" t="n">
         <v>9</v>
-      </c>
-      <c r="E51" t="n">
-        <v>21</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -3103,24 +3103,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>sheet_consumerua</t>
+          <t>sheet_EU</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>sheet_consumerua_output.xlsx</t>
+          <t>sheet_eu_output.xlsx</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>daily_variants</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5463</v>
+        <v>8868</v>
       </c>
       <c r="E52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -3132,24 +3132,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sheet_consumerua</t>
+          <t>sheet_EU</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>sheet_consumerua_output.xlsx</t>
+          <t>sheet_eu_output.xlsx</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>series_long</t>
+          <t>descriptive_stats</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16389</v>
+        <v>18</v>
       </c>
       <c r="E53" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -3161,36 +3161,36 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sheet_consumerua</t>
+          <t>sheet_EU</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>sheet_consumerua_output.xlsx</t>
+          <t>sheet_eu_output.xlsx</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>tests</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>111299</v>
       </c>
       <c r="E54" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sheet_eu</t>
+          <t>sheet_EU</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3200,14 +3200,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>series_long</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>111299</v>
+        <v>6336</v>
       </c>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3219,7 +3219,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sheet_eu</t>
+          <t>sheet_EU</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3229,43 +3229,43 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>daily_variants</t>
+          <t>tests</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>8868</v>
+        <v>18</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>sheet_eu</t>
+          <t>sheet_Novus</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>sheet_eu_output.xlsx</t>
+          <t>sheet_novus_output.xlsx</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>descriptive_stats</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>18</v>
+        <v>1530</v>
       </c>
       <c r="E57" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -3277,24 +3277,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>sheet_eu</t>
+          <t>sheet_Novus</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sheet_eu_output.xlsx</t>
+          <t>sheet_novus_output.xlsx</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>daily_variants</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>111299</v>
+        <v>8790</v>
       </c>
       <c r="E58" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3306,24 +3306,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>sheet_eu</t>
+          <t>sheet_Novus</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>sheet_eu_output.xlsx</t>
+          <t>sheet_novus_output.xlsx</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>series_long</t>
+          <t>descriptive_stats</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6336</v>
+        <v>36</v>
       </c>
       <c r="E59" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -3335,36 +3335,36 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>sheet_eu</t>
+          <t>sheet_Novus</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>sheet_eu_output.xlsx</t>
+          <t>sheet_novus_output.xlsx</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>tests</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>18</v>
+        <v>1530</v>
       </c>
       <c r="E60" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>sheet_novus</t>
+          <t>sheet_Novus</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3374,14 +3374,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>series_long</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1530</v>
+        <v>755</v>
       </c>
       <c r="E61" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sheet_novus</t>
+          <t>sheet_Novus</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3403,43 +3403,43 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>daily_variants</t>
+          <t>tests</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8790</v>
+        <v>36</v>
       </c>
       <c r="E62" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>sheet_novus</t>
+          <t>sheet_ProZorro</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>sheet_novus_output.xlsx</t>
+          <t>sheet_prozorro_output.xlsx</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>descriptive_stats</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>36</v>
+        <v>10927</v>
       </c>
       <c r="E63" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3451,24 +3451,24 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>sheet_novus</t>
+          <t>sheet_ProZorro</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>sheet_novus_output.xlsx</t>
+          <t>sheet_prozorro_output.xlsx</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>daily_variants</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1530</v>
+        <v>40843</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3480,24 +3480,24 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>sheet_novus</t>
+          <t>sheet_ProZorro</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>sheet_novus_output.xlsx</t>
+          <t>sheet_prozorro_output.xlsx</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>series_long</t>
+          <t>descriptive_stats</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>755</v>
+        <v>21</v>
       </c>
       <c r="E65" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3509,53 +3509,53 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>sheet_novus</t>
+          <t>sheet_ProZorro</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>sheet_novus_output.xlsx</t>
+          <t>sheet_prozorro_output.xlsx</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>tests</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>36</v>
+        <v>10927</v>
       </c>
       <c r="E66" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>sheet_producerua</t>
+          <t>sheet_ProZorro</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>sheet_producerua_output.xlsx</t>
+          <t>sheet_prozorro_output.xlsx</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>series_long</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10758</v>
+        <v>7613</v>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3567,36 +3567,36 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>sheet_producerua</t>
+          <t>sheet_ProZorro</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>sheet_producerua_output.xlsx</t>
+          <t>sheet_prozorro_output.xlsx</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>daily_variants</t>
+          <t>tests</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10758</v>
+        <v>21</v>
       </c>
       <c r="E68" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>sheet_producerua</t>
+          <t>sheet_ProducerUA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3606,14 +3606,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>descriptive_stats</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>18</v>
+        <v>10758</v>
       </c>
       <c r="E69" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sheet_producerua</t>
+          <t>sheet_ProducerUA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3635,14 +3635,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>daily_variants</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>10758</v>
       </c>
       <c r="E70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>sheet_producerua</t>
+          <t>sheet_ProducerUA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>series_long</t>
+          <t>descriptive_stats</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>32274</v>
+        <v>18</v>
       </c>
       <c r="E71" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -3683,7 +3683,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>sheet_producerua</t>
+          <t>sheet_ProducerUA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3693,43 +3693,43 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>tests</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>18</v>
+        <v>10758</v>
       </c>
       <c r="E72" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>sheet_prozorro</t>
+          <t>sheet_ProducerUA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>sheet_prozorro_output.xlsx</t>
+          <t>sheet_producerua_output.xlsx</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>series_long</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10927</v>
+        <v>32274</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3741,53 +3741,53 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>sheet_prozorro</t>
+          <t>sheet_ProducerUA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>sheet_prozorro_output.xlsx</t>
+          <t>sheet_producerua_output.xlsx</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>daily_variants</t>
+          <t>tests</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>40843</v>
+        <v>18</v>
       </c>
       <c r="E74" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>sheet_prozorro</t>
+          <t>sheet_Silpo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>sheet_prozorro_output.xlsx</t>
+          <t>sheet_silpo_output.xlsx</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>descriptive_stats</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>21</v>
+        <v>86765</v>
       </c>
       <c r="E75" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -3799,21 +3799,21 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>sheet_prozorro</t>
+          <t>sheet_Silpo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>sheet_prozorro_output.xlsx</t>
+          <t>sheet_silpo_output.xlsx</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>daily_variants</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10927</v>
+        <v>23691</v>
       </c>
       <c r="E76" t="n">
         <v>12</v>
@@ -3828,24 +3828,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>sheet_prozorro</t>
+          <t>sheet_Silpo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>sheet_prozorro_output.xlsx</t>
+          <t>sheet_silpo_output.xlsx</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>series_long</t>
+          <t>descriptive_stats</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>7613</v>
+        <v>36</v>
       </c>
       <c r="E77" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -3857,36 +3857,36 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>sheet_prozorro</t>
+          <t>sheet_Silpo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>sheet_prozorro_output.xlsx</t>
+          <t>sheet_silpo_output.xlsx</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>tests</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>21</v>
+        <v>86765</v>
       </c>
       <c r="E78" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>sheet_silpo</t>
+          <t>sheet_Silpo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3896,14 +3896,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>clean</t>
+          <t>series_long</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>86765</v>
+        <v>20933</v>
       </c>
       <c r="E79" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>sheet_silpo</t>
+          <t>sheet_Silpo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3925,135 +3925,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>daily_variants</t>
+          <t>tests</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>23691</v>
+        <v>36</v>
       </c>
       <c r="E80" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>sheet_silpo</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>sheet_silpo_output.xlsx</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>descriptive_stats</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>36</v>
-      </c>
-      <c r="E81" t="n">
-        <v>21</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>sheet_silpo</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>sheet_silpo_output.xlsx</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>86765</v>
-      </c>
-      <c r="E82" t="n">
-        <v>19</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>sheet_silpo</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>sheet_silpo_output.xlsx</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>series_long</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>20933</v>
-      </c>
-      <c r="E83" t="n">
-        <v>11</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>sheet_silpo</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>sheet_silpo_output.xlsx</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>36</v>
-      </c>
-      <c r="E84" t="n">
-        <v>23</v>
-      </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4068,7 +3952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4131,98 +4015,98 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sheet_cme</t>
+          <t>model_short_chain_regional</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sheet_cme_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tests</t>
+          <t>Consolidated_PreTests</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>I(1)-like share=0.33, stationary share=0.00, autocorr risk share=0.33, heterosk risk share=0.00, non-normal share=0.33, stability risk share=0.33. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
+          <t>I(1)-like share=0.00, stationary share=0.00, autocorr risk share=0.00, heterosk risk share=0.00, non-normal share=0.00, stability risk share=0.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sheet_consumerua</t>
+          <t>model_short_chain_regional</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sheet_consumerua_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tests</t>
+          <t>Consolidated_ResidualDiagnostic</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>I(1)-like share=1.00, stationary share=0.00, autocorr risk share=1.00, heterosk risk share=1.00, non-normal share=1.00, stability risk share=1.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
+          <t>I(1)-like share=0.00, stationary share=0.00, autocorr risk share=0.00, heterosk risk share=0.00, non-normal share=0.00, stability risk share=0.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sheet_eu</t>
+          <t>sheet_CME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sheet_eu_output.xlsx</t>
+          <t>sheet_cme_output.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4231,7 +4115,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>0.3333333333333333</v>
@@ -4240,10 +4124,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05555555555555555</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0.3333333333333333</v>
@@ -4253,19 +4137,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>I(1)-like share=0.33, stationary share=0.00, autocorr risk share=0.22, heterosk risk share=0.06, non-normal share=0.33, stability risk share=0.33. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
+          <t>I(1)-like share=0.33, stationary share=0.00, autocorr risk share=0.33, heterosk risk share=0.00, non-normal share=0.33, stability risk share=0.33. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sheet_novus</t>
+          <t>sheet_ConsumerUA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sheet_novus_output.xlsx</t>
+          <t>sheet_consumerua_output.xlsx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4274,41 +4158,41 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>I(1)-like share=0.00, stationary share=0.00, autocorr risk share=0.00, heterosk risk share=0.00, non-normal share=0.00, stability risk share=0.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
+          <t>I(1)-like share=1.00, stationary share=0.00, autocorr risk share=1.00, heterosk risk share=1.00, non-normal share=1.00, stability risk share=1.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sheet_producerua</t>
+          <t>sheet_EU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sheet_producerua_output.xlsx</t>
+          <t>sheet_eu_output.xlsx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4320,38 +4204,38 @@
         <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>I(1)-like share=1.00, stationary share=0.00, autocorr risk share=1.00, heterosk risk share=1.00, non-normal share=1.00, stability risk share=1.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
+          <t>I(1)-like share=0.33, stationary share=0.00, autocorr risk share=0.22, heterosk risk share=0.06, non-normal share=0.33, stability risk share=0.33. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sheet_prozorro</t>
+          <t>sheet_Novus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_prozorro_output.xlsx</t>
+          <t>sheet_novus_output.xlsx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4360,70 +4244,156 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1904761904761905</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09523809523809523</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09523809523809523</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04761904761904762</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>I(1)-like share=0.19, stationary share=0.10, autocorr risk share=0.10, heterosk risk share=0.00, non-normal share=0.05, stability risk share=0.29. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
+          <t>I(1)-like share=0.00, stationary share=0.00, autocorr risk share=0.00, heterosk risk share=0.00, non-normal share=0.00, stability risk share=0.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sheet_silpo</t>
+          <t>sheet_ProZorro</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>sheet_prozorro_output.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>tests</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>I(1)-like share=0.19, stationary share=0.10, autocorr risk share=0.10, heterosk risk share=0.00, non-normal share=0.05, stability risk share=0.29. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sheet_ProducerUA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sheet_producerua_output.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>tests</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>I(1)-like share=1.00, stationary share=0.00, autocorr risk share=1.00, heterosk risk share=1.00, non-normal share=1.00, stability risk share=1.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sheet_Silpo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>sheet_silpo_output.xlsx</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>tests</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" t="n">
         <v>36</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>I(1)-like share=0.00, stationary share=0.00, autocorr risk share=0.00, heterosk risk share=0.00, non-normal share=0.00, stability risk share=0.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks.</t>
         </is>
@@ -4440,7 +4410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4542,445 +4512,391 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9400399629337283</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.7727272727272727</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.2727272727272727</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>mean |coef|=0.9400 | positive share=0.77 | significance share (p&lt;0.05)=0.27 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>model_discounts</t>
+          <t>model_ecm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_discounts_output.xlsx</t>
+          <t>model_ecm_output.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Silpo_Transmission_PromoCtrl</t>
+          <t>ECM_Summary</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.847935761026504</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>mean |coef|=1.8479 | positive share=0.50 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>model_ecm</t>
+          <t>model_forecast_knn</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>model_ecm_output.xlsx</t>
+          <t>model_forecast_knn_output.xlsx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARDL_Summary</t>
+          <t>Synthetic_Influence_Coefficient</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9400399629337283</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7727272727272727</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.2727272727272727</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>mean |coef|=0.9400 | positive share=0.77 | significance share (p&lt;0.05)=0.27 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>mean |coef|=0.5000 | positive share=1.00 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>model_ecm</t>
+          <t>model_forecast_knn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>model_ecm_output.xlsx</t>
+          <t>model_forecast_knn_output.xlsx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ECM_Summary</t>
+          <t>Synthetic_to_Consumer_Link</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6233935610457214</v>
+        <v>0.9906802551231674</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>mean |coef|=0.6234 | positive share=0.44 | significance share (p&lt;0.05)=1.00 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>mean |coef|=0.9907 | positive share=0.33 | significance share (p&lt;0.05)=0.00 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>model_forecast_knn</t>
+          <t>model_nardl</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>model_forecast_knn_output.xlsx</t>
+          <t>model_nardl_output.xlsx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Synthetic_Influence_Coefficient</t>
+          <t>NARDL_Summary</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>mean |coef|=0.5000 | positive share=1.00 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>model_forecast_knn</t>
+          <t>model_short_chain_regional</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>model_forecast_knn_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Synthetic_to_Consumer_Link</t>
+          <t>Consolidated_ModelCoefficients</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9906802551231674</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>mean |coef|=0.9907 | positive share=0.33 | significance share (p&lt;0.05)=0.00 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>model_intersection_bidirectional</t>
+          <t>model_short_chain_regional</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>model_intersection_bidirectional_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bidirectional_Results</t>
+          <t>Consolidated_PreTests</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.9493166608329686</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.5212765957446809</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.2553191489361702</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>mean |coef|=0.9493 | positive share=0.52 | significance share (p&lt;0.05)=0.26 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>model_intersection_bidirectional</t>
+          <t>model_short_chain_regional</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>model_intersection_bidirectional_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Intersection_Combination_Detail</t>
+          <t>Consolidated_ResidualDiagnostic</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4.533354947742642</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.6875</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>mean |coef|=4.5334 | positive share=0.50 | significance share (p&lt;0.05)=0.69 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>model_intersection_bidirectional</t>
+          <t>model_vecm</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>model_intersection_bidirectional_output.xlsx</t>
+          <t>model_vecm_output.xlsx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Intersection_Combination_Summar</t>
+          <t>VECM_Summary</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3.12014259481457</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.6875</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>mean |coef|=3.1201 | positive share=0.33 | significance share (p&lt;0.05)=0.69 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>model_nardl</t>
+          <t>sheet_CME</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>model_nardl_output.xlsx</t>
+          <t>sheet_cme_output.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NARDL_Summary</t>
+          <t>tests</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.3855059551681209</v>
-      </c>
-      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.3181818181818182</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>mean |coef|=0.3855 | positive share=0.50 | significance share (p&lt;0.05)=0.32 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>significance share (p&lt;0.05)=0.50 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>model_short_chain_regional</t>
+          <t>sheet_ConsumerUA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>sheet_consumerua_output.xlsx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chain_Effects_Details</t>
+          <t>tests</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.608569635454106</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.5833333333333334</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>mean |coef|=2.6086 | positive share=0.58 | significance share (p&lt;0.05)=0.04 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>significance share (p&lt;0.05)=0.67 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>model_short_chain_regional</t>
+          <t>sheet_EU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>sheet_eu_output.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chain_Effects_Summary</t>
+          <t>tests</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2.608569635454106</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.5833333333333334</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>mean |coef|=2.6086 | positive share=0.58 | significance share (p&lt;0.05)=0.04 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>significance share (p&lt;0.05)=0.50 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>model_vecm</t>
+          <t>sheet_Novus</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>model_vecm_output.xlsx</t>
+          <t>sheet_novus_output.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VECM_Summary</t>
+          <t>tests</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>2.333333333333333</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>mean cointegration rank=2.33 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sheet_cme</t>
+          <t>sheet_ProZorro</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sheet_cme_output.xlsx</t>
+          <t>sheet_prozorro_output.xlsx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4989,29 +4905,29 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>significance share (p&lt;0.05)=0.50 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>significance share (p&lt;0.05)=0.21 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sheet_consumerua</t>
+          <t>sheet_ProducerUA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sheet_consumerua_output.xlsx</t>
+          <t>sheet_producerua_output.xlsx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5020,7 +4936,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -5037,12 +4953,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sheet_eu</t>
+          <t>sheet_Silpo</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sheet_eu_output.xlsx</t>
+          <t>sheet_silpo_output.xlsx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5051,135 +4967,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>significance share (p&lt;0.05)=0.50 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>sheet_novus</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>sheet_novus_output.xlsx</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>36</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>sheet_producerua</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>sheet_producerua_output.xlsx</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>18</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>significance share (p&lt;0.05)=0.67 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>sheet_prozorro</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>sheet_prozorro_output.xlsx</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>21</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>significance share (p&lt;0.05)=0.21 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sheet_silpo</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>sheet_silpo_output.xlsx</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>36</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
         <is>
           <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
@@ -5244,7 +5038,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_brand_region</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_brand_region</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5279,7 +5073,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_correlations_lags</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_correlations_lags</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5314,7 +5108,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_decomposition</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_decomposition</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5349,7 +5143,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/graphs_overlay_ln</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/graphs_overlay_ln</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5384,7 +5178,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_ardl</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_ardl</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5407,7 +5201,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>mean |coef|=0.9400 | positive share=0.77 | significance share (p&lt;0.05)=0.27 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_discounts</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_discounts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5442,7 +5236,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>mean |coef|=1.8479 | positive share=0.50 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>No explicit test/model tables detected; interpret via module-specific descriptive outputs.</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5248,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_ecm</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_ecm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5477,7 +5271,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>mean |coef|=0.6234 | positive share=0.44 | significance share (p&lt;0.05)=1.00 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5283,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_forecast_knn</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_forecast_knn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5524,7 +5318,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_intersection_bidirectional</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_intersection_bidirectional</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5547,7 +5341,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>mean |coef|=0.9493 | positive share=0.52 | significance share (p&lt;0.05)=0.26 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>No explicit test/model tables detected; interpret via module-specific descriptive outputs.</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5353,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_nardl</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_nardl</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5582,7 +5376,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>mean |coef|=0.3855 | positive share=0.50 | significance share (p&lt;0.05)=0.32 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
@@ -5594,30 +5388,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_short_chain_regional</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/primary_chain_summary</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_output.xlsx</t>
+          <t>primary_chain_consolidated.xlsx</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_report.pdf</t>
+          <t>primary_chain_consolidated.pdf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>model_short_chain_regional_report.md</t>
+          <t>primary_chain_consolidated.md</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>mean |coef|=2.6086 | positive share=0.58 | significance share (p&lt;0.05)=0.04 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>I(1)-like share=0.00, stationary share=0.00, autocorr risk share=0.00, heterosk risk share=0.00, non-normal share=0.00, stability risk share=0.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks. | Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5423,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/model_vecm</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/model_vecm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5652,19 +5446,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>mean cointegration rank=2.33 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>Result table has no standard coefficient/p-value columns; interpret by table-specific fields. | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sheet_cme</t>
+          <t>sheet_CME</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_cme</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_cme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5694,12 +5488,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sheet_consumerua</t>
+          <t>sheet_ConsumerUA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_consumerua</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_consumerua</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5729,12 +5523,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sheet_eu</t>
+          <t>sheet_EU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_eu</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_eu</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5764,12 +5558,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sheet_novus</t>
+          <t>sheet_Novus</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_novus</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_novus</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5799,82 +5593,82 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sheet_producerua</t>
+          <t>sheet_ProZorro</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_producerua</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_prozorro</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sheet_producerua_output.xlsx</t>
+          <t>sheet_prozorro_output.xlsx</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sheet_producerua_report.pdf</t>
+          <t>sheet_prozorro_report.pdf</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>sheet_producerua_report.md</t>
+          <t>sheet_prozorro_report.md</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I(1)-like share=1.00, stationary share=0.00, autocorr risk share=1.00, heterosk risk share=1.00, non-normal share=1.00, stability risk share=1.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks. | significance share (p&lt;0.05)=0.67 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>I(1)-like share=0.19, stationary share=0.10, autocorr risk share=0.10, heterosk risk share=0.00, non-normal share=0.05, stability risk share=0.29. Model action: cointegration/differences + lag structure + robust/HAC + stability checks. | significance share (p&lt;0.05)=0.21 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sheet_prozorro</t>
+          <t>sheet_ProducerUA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_prozorro</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_producerua</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sheet_prozorro_output.xlsx</t>
+          <t>sheet_producerua_output.xlsx</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>sheet_prozorro_report.pdf</t>
+          <t>sheet_producerua_report.pdf</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>sheet_prozorro_report.md</t>
+          <t>sheet_producerua_report.md</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I(1)-like share=0.19, stationary share=0.10, autocorr risk share=0.10, heterosk risk share=0.00, non-normal share=0.05, stability risk share=0.29. Model action: cointegration/differences + lag structure + robust/HAC + stability checks. | significance share (p&lt;0.05)=0.21 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
+          <t>I(1)-like share=1.00, stationary share=0.00, autocorr risk share=1.00, heterosk risk share=1.00, non-normal share=1.00, stability risk share=1.00. Model action: cointegration/differences + lag structure + robust/HAC + stability checks. | significance share (p&lt;0.05)=0.67 | Interpret signs/magnitudes jointly with diagnostics and sample coverage.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sheet_silpo</t>
+          <t>sheet_Silpo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/separately RW3/outputs/sheet_silpo</t>
+          <t>/Users/getapple/Documents/KSE/Master Thesis/Main materials/Model/Charniuk_Dairy_Research/outputs/sheet_silpo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
